--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amelielemay/Desktop/WaterDRoP/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697CA915-5042-D14B-B222-CD6BED35022A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9F81E2-6ADD-B54B-A378-AE06F891BA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="500" windowWidth="27620" windowHeight="18360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2900" yWindow="500" windowWidth="27620" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Key" sheetId="2" r:id="rId1"/>
@@ -10522,9 +10522,6 @@
   </si>
   <si>
     <t>U.S. Environmental Protection Agency report or literature study</t>
-  </si>
-  <si>
-    <t>European Chemicals Agency dossier accessed via the OECD eChem Portal</t>
   </si>
   <si>
     <t>PPDB</t>
@@ -11913,12 +11910,15 @@
   <si>
     <t>7.9</t>
   </si>
+  <si>
+    <t>European Chemicals Agency dossier accessed via the OECD eChem Portal (Note that the ECHA links are no longer active; they are provided only to document the original source).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -11995,6 +11995,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -12019,11 +12027,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -12039,8 +12048,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FAF88BA9-6428-454A-97CF-71C335188F9A}"/>
   </cellStyles>
@@ -12514,16 +12526,16 @@
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>3500</v>
+      <c r="B3" s="12" t="s">
+        <v>3554</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
+        <v>3500</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3501</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3502</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -12531,7 +12543,7 @@
         <v>443</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -12541,18 +12553,18 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
+        <v>3503</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>3504</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>3505</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
+        <v>3505</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>3506</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3507</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -12560,7 +12572,7 @@
         <v>154</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -12568,7 +12580,7 @@
         <v>158</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -12576,15 +12588,15 @@
         <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>3511</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>3512</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -12592,7 +12604,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -12600,7 +12612,7 @@
         <v>87</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -12608,39 +12620,39 @@
         <v>1712</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
+        <v>3515</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>3516</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>3517</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
+        <v>3517</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>3518</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>3519</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
+        <v>3520</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>3521</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>3522</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -12648,7 +12660,7 @@
         <v>1959</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -12656,7 +12668,7 @@
         <v>919</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -12664,15 +12676,15 @@
         <v>518</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
+        <v>3525</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>3526</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>3527</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -12680,7 +12692,7 @@
         <v>3298</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -12688,15 +12700,15 @@
         <v>610</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
+        <v>3529</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>3530</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>3531</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -12704,7 +12716,7 @@
         <v>939</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -12712,7 +12724,7 @@
         <v>2035</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -12720,15 +12732,15 @@
         <v>2111</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2" t="s">
+        <v>3534</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>3535</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>3536</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -12736,7 +12748,7 @@
         <v>1938</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -12744,7 +12756,7 @@
         <v>442</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -12752,7 +12764,7 @@
         <v>1027</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -12760,7 +12772,7 @@
         <v>2234</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="C36" s="4"/>
     </row>
@@ -12769,7 +12781,7 @@
         <v>3134</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="C37" s="4"/>
     </row>
@@ -12778,7 +12790,7 @@
         <v>681</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -12786,7 +12798,7 @@
         <v>643</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="C39" s="5"/>
     </row>
@@ -12795,7 +12807,7 @@
         <v>849</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -12803,7 +12815,7 @@
         <v>2326</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -12904,7 +12916,7 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -16446,22 +16458,22 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="B140" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="C140" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="D140" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="E140" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="F140" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="G140" t="s">
         <v>6</v>
@@ -24258,10 +24270,10 @@
         <v>1960</v>
       </c>
       <c r="E440" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="F440" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="G440" t="s">
         <v>443</v>
@@ -31032,22 +31044,22 @@
     </row>
     <row r="701" spans="1:8">
       <c r="A701" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="B701" t="s">
         <v>4</v>
       </c>
       <c r="C701" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="D701" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="E701" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="F701" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="G701" t="s">
         <v>6</v>
@@ -33865,6 +33877,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{5B046043-48A3-5045-93E8-5DFC5A8D641E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amelielemay/Desktop/WaterDRoP/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9F81E2-6ADD-B54B-A378-AE06F891BA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2B6DC1-232A-8444-9CD6-54D38380EAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2900" yWindow="500" windowWidth="27620" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1180" yWindow="500" windowWidth="27620" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Key" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6566" uniqueCount="3555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6567" uniqueCount="3556">
   <si>
     <t>CASRN</t>
   </si>
@@ -11911,7 +11911,31 @@
     <t>7.9</t>
   </si>
   <si>
-    <t>European Chemicals Agency dossier accessed via the OECD eChem Portal (Note that the ECHA links are no longer active; they are provided only to document the original source).</t>
+    <t xml:space="preserve">European Chemicals Agency dossier accessed via the OECD eChem Portal </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note that the ECHA links are </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>no longer active.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> They are provided only to document the original source.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -11997,11 +12021,9 @@
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
     </font>
   </fonts>
   <fills count="3">
@@ -12027,10 +12049,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -12048,11 +12069,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FAF88BA9-6428-454A-97CF-71C335188F9A}"/>
   </cellStyles>
@@ -12509,12 +12529,12 @@
     <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="9" t="s">
         <v>3495</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -12522,15 +12542,18 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>3554</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" s="11" t="s">
+        <v>3555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>3500</v>
       </c>
@@ -12538,7 +12561,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>443</v>
       </c>
@@ -12546,12 +12569,12 @@
         <v>3502</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>3503</v>
       </c>
@@ -12559,7 +12582,7 @@
         <v>3504</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>3505</v>
       </c>
@@ -12567,7 +12590,7 @@
         <v>3506</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>154</v>
       </c>
@@ -12575,7 +12598,7 @@
         <v>3507</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>158</v>
       </c>
@@ -12583,7 +12606,7 @@
         <v>3508</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -12591,7 +12614,7 @@
         <v>3509</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>3510</v>
       </c>
@@ -12599,7 +12622,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -12607,7 +12630,7 @@
         <v>3512</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>87</v>
       </c>
@@ -12916,7 +12939,7 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="12" t="s">
         <v>11</v>
       </c>
     </row>
@@ -33877,9 +33900,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{5B046043-48A3-5045-93E8-5DFC5A8D641E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
